--- a/config/excel/gacha.xlsx
+++ b/config/excel/gacha.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\go\gforgame\config\excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="item" sheetId="1" r:id="rId1"/>
@@ -41,7 +46,7 @@
     <t>品质</t>
   </si>
   <si>
-    <t>描述</t>
+    <t>奖励</t>
   </si>
   <si>
     <t>int</t>
@@ -1299,7 +1304,7 @@
     <col min="2" max="2" width="7.375" customWidth="1"/>
     <col min="3" max="3" width="11.8166666666667" customWidth="1"/>
     <col min="4" max="4" width="8.54166666666667" customWidth="1"/>
-    <col min="5" max="5" width="70.25" customWidth="1"/>
+    <col min="5" max="5" width="21.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1536,9 +1541,6 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="B20:J24">
-    <sortCondition ref="B20"/>
-  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
